--- a/data/trans_orig/P02E$contratada-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P02E$contratada-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según el tipo de ayuda al cuidado (multirrespuesta) en 2007</t>
+          <t>Hogares según el tipo de ayuda al cuidado (multirrespuesta) en 2007 (tasa de respuesta: 96,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,97 +732,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1909</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,36%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1825</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>3,61%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1883</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28137</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30046</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42508</t>
+          <t>42275</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49691</t>
+          <t>49657</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>83,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>71440</t>
+          <t>72440</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>79700</t>
+          <t>79699</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1909</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>836</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>7423</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>855</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7385</t>
+          <t>7425</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,21%</t>
         </is>
       </c>
     </row>
@@ -1071,97 +1071,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>881</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1909</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4934</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,36%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>9,76%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>881</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4672</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>5346</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>9,24%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>881</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4364</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10218</t>
+          <t>8637</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7517</t>
+          <t>7063</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1637</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12802</t>
+          <t>12081</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>128767</t>
+          <t>128036</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>148916</t>
+          <t>148429</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>76,74%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>260793</t>
+          <t>261185</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>281314</t>
+          <t>281784</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>394920</t>
+          <t>398313</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>424970</t>
+          <t>425408</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,56%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15564</t>
+          <t>16494</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34013</t>
+          <t>36000</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18925</t>
+          <t>19411</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38719</t>
+          <t>39446</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40978</t>
+          <t>40236</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>67274</t>
+          <t>66203</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,09%</t>
         </is>
       </c>
     </row>
@@ -1527,97 +1527,97 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="R11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1688</t>
+          <t>884</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12127</t>
+          <t>11327</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4317</t>
+          <t>4287</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17740</t>
+          <t>18382</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,47 +1694,47 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>4,69%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>13944</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>7274</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>23948</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
           <t>1,1%</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>4,52%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>13944</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>7777</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>24193</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>238030</t>
+          <t>239304</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>257073</t>
+          <t>256810</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>355322</t>
+          <t>355495</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>374729</t>
+          <t>376063</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>602218</t>
+          <t>601392</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>628615</t>
+          <t>628281</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,81%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10467</t>
+          <t>10527</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27344</t>
+          <t>25381</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8948</t>
+          <t>8731</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24016</t>
+          <t>23669</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>21979</t>
+          <t>22122</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>43491</t>
+          <t>44259</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -1983,97 +1983,97 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>1048</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>1967</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>5835</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="R15" s="2" t="inlineStr">
         <is>
           <t>1048</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="S15" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>5269</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>5916</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>1048</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>7118</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4517</t>
+          <t>3684</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9466</t>
+          <t>8737</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>902</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10412</t>
+          <t>11252</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>100127</t>
+          <t>99568</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>108526</t>
+          <t>108604</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>106170</t>
+          <t>105499</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>117812</t>
+          <t>117277</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>210822</t>
+          <t>209665</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>224822</t>
+          <t>225019</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,3%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9423</t>
+          <t>9091</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>836</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7597</t>
+          <t>7984</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2859</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>13039</t>
+          <t>13761</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -2439,97 +2439,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>2035</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>6183</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>5,12%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>2011</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>6182</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>7036</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>5,12%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>7219</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -2556,97 +2556,97 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>1228</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1891</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5721</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>10,53%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>8,54%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>1228</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>4980</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>5887</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>7,43%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>1228</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>6494</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12530</t>
+          <t>12157</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>55774</t>
+          <t>56890</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>65791</t>
+          <t>65956</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>72943</t>
+          <t>73194</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>82914</t>
+          <t>83116</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,83%</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5421</t>
+          <t>5794</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9938</t>
+          <t>8409</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>1054</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11030</t>
+          <t>10512</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,37%</t>
         </is>
       </c>
     </row>
@@ -2895,97 +2895,97 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>1891</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>10,53%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="R23" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>1944</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>2,9%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>1961</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5985</t>
+          <t>6144</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5244</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7788</t>
+          <t>8304</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>13,59%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5884</t>
+          <t>5842</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12460</t>
+          <t>12379</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>38185</t>
+          <t>38324</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>46032</t>
+          <t>46024</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>46323</t>
+          <t>46613</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>56652</t>
+          <t>57205</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>93,62%</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3549</t>
+          <t>3505</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6279</t>
+          <t>5452</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>814</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6887</t>
+          <t>7151</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,7%</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>5023</t>
+          <t>5705</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>4532</t>
+          <t>4453</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>881</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7473</t>
+          <t>7394</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,1%</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3586</t>
+          <t>5084</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5675</t>
+          <t>4566</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6558</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>14,83%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8087</t>
+          <t>8244</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14701</t>
+          <t>14636</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>10657</t>
+          <t>10819</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>20884</t>
+          <t>20957</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>20880</t>
+          <t>20735</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>33798</t>
+          <t>33421</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>80,29%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>868</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>7288</t>
+          <t>7387</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3418</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>12770</t>
+          <t>13800</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6269</t>
+          <t>6420</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>18762</t>
+          <t>18625</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>44,74%</t>
         </is>
       </c>
     </row>
@@ -3807,97 +3807,97 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>1706</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>10,53%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="R31" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>2103</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>8,27%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>1988</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3924,12 +3924,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>20210</t>
+          <t>19648</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>9755</t>
+          <t>10421</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>28288</t>
+          <t>28616</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>17969</t>
+          <t>18906</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>41980</t>
+          <t>41571</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>546033</t>
+          <t>542866</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>577409</t>
+          <t>575356</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4072,12 +4072,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>902148</t>
+          <t>904399</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>938991</t>
+          <t>938538</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1458464</t>
+          <t>1459284</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1506307</t>
+          <t>1507798</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,39%</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>38959</t>
+          <t>39746</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>65075</t>
+          <t>66857</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>46801</t>
+          <t>48783</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>77212</t>
+          <t>77764</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>93071</t>
+          <t>92870</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>134732</t>
+          <t>134030</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -4268,7 +4268,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>5789</t>
+          <t>6502</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4298,12 +4298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1878</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>10719</t>
+          <t>10784</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4313,7 +4313,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4333,12 +4333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2909</t>
+          <t>2875</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>13638</t>
+          <t>13372</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -4420,7 +4420,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según el tipo de ayuda al cuidado (multirrespuesta) en 2012</t>
+          <t>Hogares según el tipo de ayuda al cuidado (multirrespuesta) en 2012 (tasa de respuesta: 98,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4615,97 +4615,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1911</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,66%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1948</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1954</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32275</t>
+          <t>31727</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39975</t>
+          <t>39984</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>89666</t>
+          <t>88961</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>99617</t>
+          <t>99625</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>125251</t>
+          <t>125539</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>137767</t>
+          <t>137683</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,53%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>895</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7316</t>
+          <t>7986</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1864</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11358</t>
+          <t>11722</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3468</t>
+          <t>3815</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15084</t>
+          <t>15459</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,84%</t>
         </is>
       </c>
     </row>
@@ -4959,7 +4959,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>4222</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4082</t>
+          <t>5096</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6930</t>
+          <t>6120</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>920</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6747</t>
+          <t>7489</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12353</t>
+          <t>12572</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>1916</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14742</t>
+          <t>14698</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>187190</t>
+          <t>187751</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>202938</t>
+          <t>202972</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>340386</t>
+          <t>341732</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>364681</t>
+          <t>365788</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>535779</t>
+          <t>534847</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>563845</t>
+          <t>562685</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,04%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7708</t>
+          <t>7878</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21746</t>
+          <t>21756</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5312,7 +5312,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20309</t>
+          <t>20298</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41459</t>
+          <t>41673</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32180</t>
+          <t>31689</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>56093</t>
+          <t>57141</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,45%</t>
         </is>
       </c>
     </row>
@@ -5415,7 +5415,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5490</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>934</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8468</t>
+          <t>8500</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9454</t>
+          <t>9899</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2787</t>
+          <t>2905</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15805</t>
+          <t>16918</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2997</t>
+          <t>3733</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16560</t>
+          <t>17076</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8448</t>
+          <t>8420</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>26326</t>
+          <t>27000</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>369842</t>
+          <t>371275</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>393824</t>
+          <t>393524</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>529722</t>
+          <t>531185</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>552536</t>
+          <t>553347</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>909202</t>
+          <t>910903</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>941282</t>
+          <t>940743</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,17%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14145</t>
+          <t>12858</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32924</t>
+          <t>31717</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14531</t>
+          <t>14555</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>34174</t>
+          <t>32213</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5803,47 +5803,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
+          <t>5,61%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>43855</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>32598</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>58774</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>4,44%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>5,95%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>43855</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>31497</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>56935</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>4,44%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>3,19%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5612</t>
+          <t>6279</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6482</t>
+          <t>7025</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>977</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>9655</t>
+          <t>9333</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>951</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9300</t>
+          <t>8418</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10821</t>
+          <t>9750</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3215</t>
+          <t>3252</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15381</t>
+          <t>15352</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>207627</t>
+          <t>208170</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>222109</t>
+          <t>221641</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>237782</t>
+          <t>238976</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>253167</t>
+          <t>254030</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>453620</t>
+          <t>453529</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>472503</t>
+          <t>472399</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,34%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12796</t>
+          <t>11632</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4359</t>
+          <t>4331</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16356</t>
+          <t>16446</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8330</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>23906</t>
+          <t>23879</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -6322,12 +6322,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>982</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8975</t>
+          <t>9019</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6105</t>
+          <t>6568</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6392,12 +6392,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1123</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9945</t>
+          <t>9918</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6407,12 +6407,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2499</t>
+          <t>2954</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13688</t>
+          <t>14400</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2960</t>
+          <t>2959</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13338</t>
+          <t>14252</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6529,7 +6529,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,52%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>37174</t>
+          <t>37375</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>46979</t>
+          <t>46948</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>77358</t>
+          <t>75899</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>91694</t>
+          <t>91372</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>116802</t>
+          <t>118542</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>135663</t>
+          <t>135802</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,73%</t>
         </is>
       </c>
     </row>
@@ -6670,7 +6670,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7317</t>
+          <t>7650</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6685,7 +6685,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9832</t>
+          <t>10520</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2224</t>
+          <t>2207</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12775</t>
+          <t>13289</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,88%</t>
         </is>
       </c>
     </row>
@@ -6778,12 +6778,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1016</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9517</t>
+          <t>8887</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6793,12 +6793,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1148</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9843</t>
+          <t>10053</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6828,12 +6828,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3980</t>
+          <t>3291</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>16441</t>
+          <t>15345</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6863,12 +6863,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,25%</t>
         </is>
       </c>
     </row>
@@ -6900,7 +6900,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>6464</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6935,7 +6935,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4011</t>
+          <t>5108</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>969</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>8012</t>
+          <t>8412</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>12,09%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10350</t>
+          <t>10281</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19257</t>
+          <t>19221</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>35205</t>
+          <t>34592</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>44365</t>
+          <t>44341</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>48475</t>
+          <t>48289</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>61241</t>
+          <t>60801</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>87,39%</t>
         </is>
       </c>
     </row>
@@ -7126,7 +7126,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4084</t>
+          <t>5520</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>927</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7880</t>
+          <t>7456</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8823</t>
+          <t>9686</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>13,92%</t>
         </is>
       </c>
     </row>
@@ -7234,12 +7234,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>8673</t>
+          <t>8778</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>948</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>7528</t>
+          <t>7881</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7284,12 +7284,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7304,12 +7304,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>3039</t>
+          <t>2965</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>12875</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7319,12 +7319,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>20,12%</t>
         </is>
       </c>
     </row>
@@ -7356,7 +7356,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4439</t>
+          <t>4810</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2178</t>
+          <t>2101</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>11176</t>
+          <t>11252</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2267</t>
+          <t>2942</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>12862</t>
+          <t>13399</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,85%</t>
         </is>
       </c>
     </row>
@@ -7464,12 +7464,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3771</t>
+          <t>3802</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12666</t>
+          <t>12687</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7499,12 +7499,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>17131</t>
+          <t>16841</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>30549</t>
+          <t>30004</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7534,12 +7534,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>25268</t>
+          <t>24537</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>39833</t>
+          <t>39516</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7549,12 +7549,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>70,34%</t>
         </is>
       </c>
     </row>
@@ -7577,12 +7577,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1138</t>
+          <t>1140</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>9474</t>
+          <t>9611</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>64,29%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3222</t>
+          <t>3180</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>13312</t>
+          <t>13924</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7647,12 +7647,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>5608</t>
+          <t>6282</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>19672</t>
+          <t>19404</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7662,12 +7662,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>34,54%</t>
         </is>
       </c>
     </row>
@@ -7695,7 +7695,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5362</t>
+          <t>5213</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7710,7 +7710,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7725,12 +7725,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2109</t>
+          <t>2083</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>11096</t>
+          <t>11129</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7740,12 +7740,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7760,12 +7760,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t>2964</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>12185</t>
+          <t>13097</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>23,31%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>9777</t>
+          <t>9537</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>27556</t>
+          <t>27679</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>18523</t>
+          <t>19166</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>42096</t>
+          <t>41051</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>33115</t>
+          <t>32835</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>61772</t>
+          <t>61688</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>881615</t>
+          <t>880605</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>916099</t>
+          <t>917356</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7955,12 +7955,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1366090</t>
+          <t>1367614</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1411974</t>
+          <t>1410901</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7990,12 +7990,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2260750</t>
+          <t>2263198</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>2318630</t>
+          <t>2319630</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8005,12 +8005,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,72%</t>
         </is>
       </c>
     </row>
@@ -8033,12 +8033,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>37619</t>
+          <t>38149</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>67032</t>
+          <t>66076</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8068,12 +8068,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>63709</t>
+          <t>63294</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>100977</t>
+          <t>98066</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>110604</t>
+          <t>109007</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>158601</t>
+          <t>156063</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8118,12 +8118,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -8146,12 +8146,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>9290</t>
+          <t>9346</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>24976</t>
+          <t>26343</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8161,12 +8161,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>12289</t>
+          <t>12338</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>29755</t>
+          <t>30853</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8216,12 +8216,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>25836</t>
+          <t>25363</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>49672</t>
+          <t>50094</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8231,12 +8231,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según el tipo de ayuda al cuidado (multirrespuesta) en 2016</t>
+          <t>Hogares según el tipo de ayuda al cuidado (multirrespuesta) en 2016 (tasa de respuesta: 93,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8498,97 +8498,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2048</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5,03%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1872</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,08%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1942</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8611,12 +8611,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31157</t>
+          <t>31502</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39687</t>
+          <t>39689</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8626,7 +8626,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -8646,12 +8646,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>67678</t>
+          <t>67058</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>81045</t>
+          <t>81126</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8661,12 +8661,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>74,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8681,12 +8681,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>103067</t>
+          <t>103738</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>118588</t>
+          <t>118962</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8696,12 +8696,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>91,07%</t>
         </is>
       </c>
     </row>
@@ -8729,7 +8729,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6327</t>
+          <t>6333</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8744,7 +8744,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8759,12 +8759,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8823</t>
+          <t>8742</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22190</t>
+          <t>22810</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8794,12 +8794,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10633</t>
+          <t>10360</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>25267</t>
+          <t>24906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8809,12 +8809,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,07%</t>
         </is>
       </c>
     </row>
@@ -8842,7 +8842,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6511</t>
+          <t>6679</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8857,7 +8857,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8872,62 +8872,62 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>2176</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1872</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>7542</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,08%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>2176</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>7479</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6049</t>
+          <t>5146</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8989,62 +8989,62 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1016</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1871</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>5120</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1016</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>6136</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -9067,12 +9067,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>153307</t>
+          <t>153710</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>167236</t>
+          <t>167539</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9102,12 +9102,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>255948</t>
+          <t>257071</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>276038</t>
+          <t>275887</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9117,12 +9117,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9137,12 +9137,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>417722</t>
+          <t>416899</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>440170</t>
+          <t>440757</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9152,12 +9152,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,44%</t>
         </is>
       </c>
     </row>
@@ -9180,12 +9180,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3866</t>
+          <t>3899</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15134</t>
+          <t>15597</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9195,12 +9195,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9215,12 +9215,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17365</t>
+          <t>17516</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37455</t>
+          <t>36332</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9250,12 +9250,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23598</t>
+          <t>23719</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45523</t>
+          <t>45432</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9265,12 +9265,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -9298,7 +9298,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6906</t>
+          <t>6677</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9313,7 +9313,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9328,62 +9328,62 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1936</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>1871</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>5938</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1936</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>6626</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -9410,12 +9410,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>1632</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10646</t>
+          <t>11468</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9425,12 +9425,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9445,12 +9445,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4699</t>
+          <t>4713</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17032</t>
+          <t>16738</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9460,12 +9460,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9480,12 +9480,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7243</t>
+          <t>7954</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>22992</t>
+          <t>23877</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9495,12 +9495,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -9523,12 +9523,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>277428</t>
+          <t>276003</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>296816</t>
+          <t>295651</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>344633</t>
+          <t>347004</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>372516</t>
+          <t>373128</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9573,12 +9573,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9593,12 +9593,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>629544</t>
+          <t>632398</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>663455</t>
+          <t>662956</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9608,12 +9608,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,19%</t>
         </is>
       </c>
     </row>
@@ -9636,12 +9636,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11244</t>
+          <t>11070</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27185</t>
+          <t>28888</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9651,12 +9651,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9671,12 +9671,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>26252</t>
+          <t>25787</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>49013</t>
+          <t>49693</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9686,12 +9686,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9706,12 +9706,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>42037</t>
+          <t>41667</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>70133</t>
+          <t>69004</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9721,12 +9721,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,6%</t>
         </is>
       </c>
     </row>
@@ -9754,7 +9754,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5759</t>
+          <t>5226</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9769,7 +9769,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9789,7 +9789,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5251</t>
+          <t>5456</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9804,7 +9804,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9824,7 +9824,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6792</t>
+          <t>6614</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -9866,12 +9866,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3165</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13787</t>
+          <t>14240</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9881,12 +9881,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9622</t>
+          <t>10761</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9936,12 +9936,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5388</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19215</t>
+          <t>20492</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9951,12 +9951,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -9979,12 +9979,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>134256</t>
+          <t>134781</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>149246</t>
+          <t>148617</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9994,12 +9994,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10014,12 +10014,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>159601</t>
+          <t>158970</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>174194</t>
+          <t>173839</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10029,12 +10029,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10049,12 +10049,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>299072</t>
+          <t>298977</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>320366</t>
+          <t>319816</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10064,12 +10064,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,3%</t>
         </is>
       </c>
     </row>
@@ -10092,12 +10092,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3225</t>
+          <t>3236</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14316</t>
+          <t>14654</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>3245</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15399</t>
+          <t>15911</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10142,12 +10142,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>9322</t>
+          <t>8497</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>26003</t>
+          <t>25323</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10177,12 +10177,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -10205,12 +10205,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10240,12 +10240,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>904</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7898</t>
+          <t>7805</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10260,7 +10260,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10275,12 +10275,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>913</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7939</t>
+          <t>8737</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10290,12 +10290,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -10327,7 +10327,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7671</t>
+          <t>6764</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10342,7 +10342,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4155</t>
+          <t>4720</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10377,7 +10377,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>968</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8492</t>
+          <t>8511</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10407,12 +10407,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -10435,12 +10435,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>30326</t>
+          <t>30392</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>39111</t>
+          <t>39136</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10450,12 +10450,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10470,12 +10470,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>37634</t>
+          <t>37607</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>50535</t>
+          <t>50068</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10485,12 +10485,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>66,23%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10505,12 +10505,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>72022</t>
+          <t>71877</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>87476</t>
+          <t>87072</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10520,12 +10520,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>74,08%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>89,75%</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5685</t>
+          <t>5316</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10568,7 +10568,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2592</t>
+          <t>3014</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13277</t>
+          <t>13431</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10598,12 +10598,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10618,12 +10618,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3222</t>
+          <t>3309</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14553</t>
+          <t>14496</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10633,12 +10633,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,94%</t>
         </is>
       </c>
     </row>
@@ -10666,7 +10666,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6653</t>
+          <t>6613</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>1111</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9842</t>
+          <t>10003</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10716,7 +10716,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3066</t>
+          <t>2963</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>13269</t>
+          <t>13568</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,98%</t>
         </is>
       </c>
     </row>
@@ -10783,7 +10783,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4801</t>
+          <t>4772</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10798,7 +10798,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10813,12 +10813,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1076</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9010</t>
+          <t>10632</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10828,12 +10828,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10848,12 +10848,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>1983</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>11686</t>
+          <t>11310</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10863,12 +10863,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>19,6%</t>
         </is>
       </c>
     </row>
@@ -10891,12 +10891,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13036</t>
+          <t>13188</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20262</t>
+          <t>20257</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10906,12 +10906,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>62,07%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10926,12 +10926,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>24588</t>
+          <t>24043</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>34367</t>
+          <t>34396</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10941,12 +10941,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10961,12 +10961,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>40802</t>
+          <t>40718</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>52605</t>
+          <t>51956</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10976,12 +10976,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>90,05%</t>
         </is>
       </c>
     </row>
@@ -11009,7 +11009,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6116</t>
+          <t>6201</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11024,7 +11024,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11044,7 +11044,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4433</t>
+          <t>5171</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11059,7 +11059,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11074,12 +11074,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>967</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8129</t>
+          <t>8797</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11089,12 +11089,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>15,25%</t>
         </is>
       </c>
     </row>
@@ -11122,7 +11122,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4817</t>
+          <t>5106</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11137,7 +11137,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -11157,7 +11157,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>5146</t>
+          <t>5266</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -11172,7 +11172,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -11192,7 +11192,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6308</t>
+          <t>6517</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -11207,7 +11207,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,3%</t>
         </is>
       </c>
     </row>
@@ -11239,7 +11239,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4460</t>
+          <t>4409</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11254,7 +11254,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11269,12 +11269,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>10962</t>
+          <t>10326</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11284,12 +11284,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11304,12 +11304,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>1582</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>11032</t>
+          <t>11743</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11319,12 +11319,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>20,48%</t>
         </is>
       </c>
     </row>
@@ -11347,12 +11347,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4992</t>
+          <t>4774</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>11110</t>
+          <t>11278</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11362,12 +11362,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -11382,12 +11382,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>19311</t>
+          <t>19546</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>34537</t>
+          <t>34149</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -11397,12 +11397,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -11417,12 +11417,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>27793</t>
+          <t>28252</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>43365</t>
+          <t>44555</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -11432,12 +11432,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>49,26%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>77,69%</t>
         </is>
       </c>
     </row>
@@ -11460,12 +11460,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1570</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11475,12 +11475,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11495,12 +11495,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>6035</t>
+          <t>6059</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>18533</t>
+          <t>20483</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11510,12 +11510,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11530,12 +11530,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>5736</t>
+          <t>5947</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>20222</t>
+          <t>19629</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11545,12 +11545,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>34,23%</t>
         </is>
       </c>
     </row>
@@ -11578,7 +11578,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6199</t>
+          <t>5935</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11593,7 +11593,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11613,7 +11613,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>8053</t>
+          <t>6760</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11628,7 +11628,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11643,12 +11643,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>860</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>9916</t>
+          <t>10188</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11658,12 +11658,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,76%</t>
         </is>
       </c>
     </row>
@@ -11690,12 +11690,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>10375</t>
+          <t>10492</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>27925</t>
+          <t>28417</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11705,12 +11705,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11725,12 +11725,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>14305</t>
+          <t>14456</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>33665</t>
+          <t>34645</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11740,12 +11740,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11760,12 +11760,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>29124</t>
+          <t>30033</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>54874</t>
+          <t>55725</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11775,12 +11775,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -11803,12 +11803,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>675488</t>
+          <t>675867</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>705880</t>
+          <t>707739</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11818,12 +11818,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11838,12 +11838,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>950221</t>
+          <t>951264</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>995994</t>
+          <t>995468</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11853,12 +11853,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -11873,12 +11873,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1638097</t>
+          <t>1636825</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1689040</t>
+          <t>1689541</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -11888,12 +11888,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,46%</t>
         </is>
       </c>
     </row>
@@ -11916,12 +11916,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>27861</t>
+          <t>27325</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>51102</t>
+          <t>52759</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -11931,12 +11931,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -11951,12 +11951,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>85700</t>
+          <t>86790</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>126184</t>
+          <t>125425</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -11966,12 +11966,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -11986,12 +11986,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>121619</t>
+          <t>122174</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>169745</t>
+          <t>171046</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12001,12 +12001,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -12029,12 +12029,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>5209</t>
+          <t>5085</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>18585</t>
+          <t>18973</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12044,12 +12044,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12064,12 +12064,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>5172</t>
+          <t>5318</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>18929</t>
+          <t>19067</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12079,12 +12079,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12099,12 +12099,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>12635</t>
+          <t>13685</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>31076</t>
+          <t>32176</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -12114,12 +12114,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P02E$contratada-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P02E$contratada-Edad-trans_orig.xlsx
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42275</t>
+          <t>42053</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49657</t>
+          <t>49670</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>72440</t>
+          <t>71593</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>79699</t>
+          <t>79630</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,79%</t>
         </is>
       </c>
     </row>
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>836</t>
+          <t>852</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7423</t>
+          <t>7425</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>847</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7425</t>
+          <t>7948</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4934</t>
+          <t>4354</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5346</t>
+          <t>5261</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8637</t>
+          <t>9486</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7063</t>
+          <t>7371</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12081</t>
+          <t>12096</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>128036</t>
+          <t>128736</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>148429</t>
+          <t>148250</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>77,16%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>261185</t>
+          <t>261631</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>281784</t>
+          <t>282416</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>398313</t>
+          <t>397683</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>425408</t>
+          <t>425353</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,55%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16494</t>
+          <t>16076</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36000</t>
+          <t>34293</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19411</t>
+          <t>19018</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39446</t>
+          <t>39069</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40236</t>
+          <t>40372</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>66203</t>
+          <t>66676</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>892</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11327</t>
+          <t>12601</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4287</t>
+          <t>4322</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18382</t>
+          <t>17415</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7274</t>
+          <t>6984</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>23948</t>
+          <t>22589</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>239304</t>
+          <t>239739</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>256810</t>
+          <t>257071</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>355495</t>
+          <t>354876</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>376063</t>
+          <t>374589</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>601392</t>
+          <t>602451</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>628281</t>
+          <t>628601</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,85%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10527</t>
+          <t>10520</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25381</t>
+          <t>25026</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8731</t>
+          <t>8793</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23669</t>
+          <t>24427</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>22122</t>
+          <t>22519</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>44259</t>
+          <t>43996</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5835</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>6397</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3684</t>
+          <t>4577</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8737</t>
+          <t>10060</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>898</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11252</t>
+          <t>9274</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>99568</t>
+          <t>99602</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>108604</t>
+          <t>108504</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>105499</t>
+          <t>106044</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>117277</t>
+          <t>117740</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>209665</t>
+          <t>211213</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>225019</t>
+          <t>224356</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,01%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9091</t>
+          <t>10395</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>836</t>
+          <t>844</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7984</t>
+          <t>8552</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2859</t>
+          <t>2916</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>13761</t>
+          <t>13954</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6183</t>
+          <t>6095</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7036</t>
+          <t>6141</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5721</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5887</t>
+          <t>7532</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12157</t>
+          <t>12180</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>56890</t>
+          <t>56675</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>65956</t>
+          <t>65951</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>73194</t>
+          <t>72733</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>83116</t>
+          <t>82878</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,55%</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5794</t>
+          <t>5771</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8409</t>
+          <t>8184</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1054</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10512</t>
+          <t>10517</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,38%</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6144</t>
+          <t>6022</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5244</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>1031</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>8304</t>
+          <t>8283</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,56%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5842</t>
+          <t>5711</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12379</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>38324</t>
+          <t>37462</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>46024</t>
+          <t>45885</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>46613</t>
+          <t>46066</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>57205</t>
+          <t>57191</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,59%</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3505</t>
+          <t>3525</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5452</t>
+          <t>5740</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>814</t>
+          <t>805</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7151</t>
+          <t>6998</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,45%</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>5705</t>
+          <t>6246</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>44,07%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>4453</t>
+          <t>4502</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>887</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7394</t>
+          <t>6977</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,42%</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5084</t>
+          <t>3911</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4566</t>
+          <t>5695</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>6207</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,91%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8244</t>
+          <t>8020</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14636</t>
+          <t>14548</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>49,51%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>10819</t>
+          <t>11181</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>20957</t>
+          <t>20925</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>20735</t>
+          <t>21152</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>33421</t>
+          <t>33693</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>80,94%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>864</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>7387</t>
+          <t>7513</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>3442</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>13800</t>
+          <t>12777</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6420</t>
+          <t>6650</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>18625</t>
+          <t>18233</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>43,8%</t>
         </is>
       </c>
     </row>
@@ -3924,12 +3924,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5776</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>19648</t>
+          <t>21178</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>10421</t>
+          <t>9967</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>28616</t>
+          <t>28037</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>18906</t>
+          <t>19499</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>41571</t>
+          <t>43188</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>542866</t>
+          <t>545566</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>575356</t>
+          <t>576200</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4072,12 +4072,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>904399</t>
+          <t>903129</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>938538</t>
+          <t>938878</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1459284</t>
+          <t>1458314</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1507798</t>
+          <t>1506480</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,31%</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>39746</t>
+          <t>38436</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>66857</t>
+          <t>66471</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>48783</t>
+          <t>48958</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>77764</t>
+          <t>79429</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>92870</t>
+          <t>92771</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>134030</t>
+          <t>134876</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -4268,7 +4268,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>6502</t>
+          <t>6168</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4298,12 +4298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1897</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>10784</t>
+          <t>11091</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4313,12 +4313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4333,12 +4333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2875</t>
+          <t>2810</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>13372</t>
+          <t>13528</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4348,12 +4348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31727</t>
+          <t>32341</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39984</t>
+          <t>40019</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>88961</t>
+          <t>89520</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>125539</t>
+          <t>125328</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>137683</t>
+          <t>137701</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,54%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>886</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7986</t>
+          <t>7309</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1856</t>
+          <t>1857</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11722</t>
+          <t>10788</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3815</t>
+          <t>3777</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15459</t>
+          <t>14927</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,47%</t>
         </is>
       </c>
     </row>
@@ -4959,7 +4959,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4222</t>
+          <t>5163</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5096</t>
+          <t>5054</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6120</t>
+          <t>6059</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>930</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7489</t>
+          <t>8067</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12572</t>
+          <t>12437</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1916</t>
+          <t>1906</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14698</t>
+          <t>14678</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>187751</t>
+          <t>186921</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>202972</t>
+          <t>202738</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>341732</t>
+          <t>340910</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>365788</t>
+          <t>365056</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>534847</t>
+          <t>535735</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>562685</t>
+          <t>564655</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,36%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7878</t>
+          <t>7908</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21756</t>
+          <t>22582</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20298</t>
+          <t>20285</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41673</t>
+          <t>41382</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5347,47 +5347,47 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
+          <t>5,19%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>10,6%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>43176</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>31458</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>56834</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>7,14%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>5,2%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>10,67%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>43176</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>31689</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>57141</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>7,14%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>5,24%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -5415,7 +5415,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>5441</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>921</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8500</t>
+          <t>8167</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1143</t>
+          <t>1843</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9899</t>
+          <t>11299</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2905</t>
+          <t>2857</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16918</t>
+          <t>16623</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3733</t>
+          <t>2951</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17076</t>
+          <t>16359</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8420</t>
+          <t>8688</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>27000</t>
+          <t>28293</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>371275</t>
+          <t>371308</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>393524</t>
+          <t>393487</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>531185</t>
+          <t>530531</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>553347</t>
+          <t>553336</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>910903</t>
+          <t>908071</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>940743</t>
+          <t>940077</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,1%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12858</t>
+          <t>13752</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>31717</t>
+          <t>30818</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14555</t>
+          <t>13974</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>32213</t>
+          <t>33616</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>32598</t>
+          <t>31881</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>58774</t>
+          <t>58338</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6279</t>
+          <t>6413</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7025</t>
+          <t>6982</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>924</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>9333</t>
+          <t>9604</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5951,12 +5951,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>963</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8418</t>
+          <t>8520</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>1068</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9750</t>
+          <t>10823</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3252</t>
+          <t>3072</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15352</t>
+          <t>13974</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>208170</t>
+          <t>207685</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>221641</t>
+          <t>221698</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>238976</t>
+          <t>239220</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>254030</t>
+          <t>254155</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>453529</t>
+          <t>452708</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>472399</t>
+          <t>472671</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,4%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11632</t>
+          <t>12122</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4331</t>
+          <t>3438</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16446</t>
+          <t>16419</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>8481</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>23879</t>
+          <t>23754</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -6322,12 +6322,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>963</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9019</t>
+          <t>8958</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6337,12 +6337,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6568</t>
+          <t>5201</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6392,12 +6392,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>1121</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9918</t>
+          <t>10452</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6407,12 +6407,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2954</t>
+          <t>2917</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>14400</t>
+          <t>13851</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2959</t>
+          <t>2932</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14252</t>
+          <t>14269</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,53%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>37375</t>
+          <t>36039</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>46948</t>
+          <t>46242</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>75899</t>
+          <t>76028</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>91372</t>
+          <t>91228</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>75,5%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>118542</t>
+          <t>118452</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>135802</t>
+          <t>136586</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,14%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>91,25%</t>
         </is>
       </c>
     </row>
@@ -6670,7 +6670,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7650</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6685,7 +6685,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10520</t>
+          <t>10455</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>2245</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13289</t>
+          <t>12852</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,59%</t>
         </is>
       </c>
     </row>
@@ -6778,12 +6778,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8887</t>
+          <t>9550</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6793,12 +6793,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1148</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10053</t>
+          <t>10029</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6828,12 +6828,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3291</t>
+          <t>3960</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>15345</t>
+          <t>15796</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6863,12 +6863,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,55%</t>
         </is>
       </c>
     </row>
@@ -6900,7 +6900,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6464</t>
+          <t>7468</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6935,7 +6935,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5108</t>
+          <t>4932</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>964</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>8412</t>
+          <t>8234</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,83%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10281</t>
+          <t>9602</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19221</t>
+          <t>19140</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>34592</t>
+          <t>34597</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>44341</t>
+          <t>44313</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>48289</t>
+          <t>48063</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>60801</t>
+          <t>61491</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>88,38%</t>
         </is>
       </c>
     </row>
@@ -7126,7 +7126,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5520</t>
+          <t>4067</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>935</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7456</t>
+          <t>8098</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>960</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>9686</t>
+          <t>8911</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>12,81%</t>
         </is>
       </c>
     </row>
@@ -7234,12 +7234,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>8778</t>
+          <t>8559</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>946</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>7881</t>
+          <t>7971</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7284,12 +7284,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7304,12 +7304,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2965</t>
+          <t>3068</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>13162</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7319,12 +7319,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>18,92%</t>
         </is>
       </c>
     </row>
@@ -7356,7 +7356,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4810</t>
+          <t>4427</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2101</t>
+          <t>2121</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>11252</t>
+          <t>11011</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2942</t>
+          <t>3089</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>13399</t>
+          <t>12963</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,07%</t>
         </is>
       </c>
     </row>
@@ -7464,12 +7464,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3802</t>
+          <t>4292</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12687</t>
+          <t>12645</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7499,12 +7499,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>16841</t>
+          <t>17902</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>30004</t>
+          <t>29758</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7534,12 +7534,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>24537</t>
+          <t>24724</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>39516</t>
+          <t>40829</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7549,12 +7549,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>72,67%</t>
         </is>
       </c>
     </row>
@@ -7577,12 +7577,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1140</t>
+          <t>1144</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>9611</t>
+          <t>9797</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3180</t>
+          <t>3306</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>13924</t>
+          <t>13309</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7647,12 +7647,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6282</t>
+          <t>5669</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>19404</t>
+          <t>19140</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7662,12 +7662,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,07%</t>
         </is>
       </c>
     </row>
@@ -7695,7 +7695,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5213</t>
+          <t>4525</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7710,7 +7710,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7725,12 +7725,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2083</t>
+          <t>2075</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>11129</t>
+          <t>10862</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7740,12 +7740,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7760,12 +7760,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2964</t>
+          <t>2247</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>13097</t>
+          <t>13148</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,4%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>9537</t>
+          <t>9748</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>27679</t>
+          <t>28174</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>19166</t>
+          <t>19027</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>41051</t>
+          <t>41013</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>32835</t>
+          <t>32198</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>61688</t>
+          <t>61828</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>880605</t>
+          <t>881128</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>917356</t>
+          <t>917470</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7955,12 +7955,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1367614</t>
+          <t>1366515</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1410901</t>
+          <t>1409518</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7990,12 +7990,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2263198</t>
+          <t>2259547</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>2319630</t>
+          <t>2316987</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8005,12 +8005,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,62%</t>
         </is>
       </c>
     </row>
@@ -8033,12 +8033,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>38149</t>
+          <t>38440</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>66076</t>
+          <t>67796</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8068,12 +8068,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>63294</t>
+          <t>63874</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>98066</t>
+          <t>100401</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>109007</t>
+          <t>111033</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>156063</t>
+          <t>156376</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8118,12 +8118,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -8146,12 +8146,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>9346</t>
+          <t>9871</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>26343</t>
+          <t>25870</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8161,12 +8161,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>12338</t>
+          <t>12014</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>30853</t>
+          <t>29190</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8196,12 +8196,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8216,12 +8216,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>25363</t>
+          <t>25513</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>50094</t>
+          <t>49172</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8231,12 +8231,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -8611,12 +8611,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31502</t>
+          <t>31301</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39689</t>
+          <t>39669</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8646,12 +8646,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>67058</t>
+          <t>67584</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>81126</t>
+          <t>81023</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8661,12 +8661,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8681,12 +8681,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>103738</t>
+          <t>102786</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>118962</t>
+          <t>118226</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8696,12 +8696,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>90,51%</t>
         </is>
       </c>
     </row>
@@ -8729,7 +8729,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>6563</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8744,7 +8744,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8759,12 +8759,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8742</t>
+          <t>8845</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22810</t>
+          <t>22284</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8794,12 +8794,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10360</t>
+          <t>10587</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>24906</t>
+          <t>24612</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8809,12 +8809,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,84%</t>
         </is>
       </c>
     </row>
@@ -8842,7 +8842,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6679</t>
+          <t>7301</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8857,7 +8857,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8912,7 +8912,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7542</t>
+          <t>8528</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8927,7 +8927,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5146</t>
+          <t>5128</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9029,7 +9029,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5120</t>
+          <t>5353</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -9067,12 +9067,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>153710</t>
+          <t>154876</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>167539</t>
+          <t>167557</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9102,12 +9102,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>257071</t>
+          <t>256469</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>275887</t>
+          <t>276280</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9117,12 +9117,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9137,12 +9137,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>416899</t>
+          <t>417420</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>440757</t>
+          <t>439967</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9152,12 +9152,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,27%</t>
         </is>
       </c>
     </row>
@@ -9180,12 +9180,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3899</t>
+          <t>3749</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15597</t>
+          <t>14913</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9195,12 +9195,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9215,12 +9215,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17516</t>
+          <t>17123</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36332</t>
+          <t>36934</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9250,12 +9250,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23719</t>
+          <t>23831</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45432</t>
+          <t>46107</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9265,12 +9265,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,88%</t>
         </is>
       </c>
     </row>
@@ -9298,7 +9298,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6677</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9313,7 +9313,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9368,7 +9368,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5938</t>
+          <t>6011</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9383,7 +9383,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -9410,12 +9410,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1632</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11468</t>
+          <t>12619</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9425,12 +9425,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9445,12 +9445,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4713</t>
+          <t>4373</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16738</t>
+          <t>16225</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9460,12 +9460,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9480,12 +9480,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7954</t>
+          <t>7173</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>23877</t>
+          <t>22634</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9495,12 +9495,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -9523,12 +9523,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>276003</t>
+          <t>278136</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>295651</t>
+          <t>296212</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>347004</t>
+          <t>348054</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>373128</t>
+          <t>373776</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9573,12 +9573,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9593,12 +9593,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>632398</t>
+          <t>632481</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>662956</t>
+          <t>662797</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9608,12 +9608,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,17%</t>
         </is>
       </c>
     </row>
@@ -9636,12 +9636,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11070</t>
+          <t>11489</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28888</t>
+          <t>28312</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9651,12 +9651,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9671,12 +9671,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25787</t>
+          <t>25703</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>49693</t>
+          <t>49016</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9686,12 +9686,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9706,12 +9706,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>41667</t>
+          <t>42511</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>69004</t>
+          <t>70128</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9721,12 +9721,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -9754,7 +9754,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5226</t>
+          <t>5704</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9769,7 +9769,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9789,7 +9789,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5456</t>
+          <t>4015</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9804,7 +9804,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9824,7 +9824,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6614</t>
+          <t>7198</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -9866,12 +9866,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3114</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14240</t>
+          <t>14744</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9881,12 +9881,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9901,12 +9901,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10761</t>
+          <t>9826</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9936,12 +9936,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>5435</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20492</t>
+          <t>19276</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9951,12 +9951,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -9979,12 +9979,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>134781</t>
+          <t>135265</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>148617</t>
+          <t>149572</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9994,12 +9994,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10014,12 +10014,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>158970</t>
+          <t>158672</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>173839</t>
+          <t>174713</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10029,12 +10029,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10049,12 +10049,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>298977</t>
+          <t>299268</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>319816</t>
+          <t>320258</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10064,12 +10064,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,43%</t>
         </is>
       </c>
     </row>
@@ -10092,12 +10092,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>3159</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14654</t>
+          <t>13917</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10107,12 +10107,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3245</t>
+          <t>3893</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15911</t>
+          <t>16571</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10142,12 +10142,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8497</t>
+          <t>9243</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>25323</t>
+          <t>26035</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10177,12 +10177,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,68%</t>
         </is>
       </c>
     </row>
@@ -10240,12 +10240,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>910</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7805</t>
+          <t>7857</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10260,7 +10260,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10275,12 +10275,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>909</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8737</t>
+          <t>8662</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10295,7 +10295,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -10327,7 +10327,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6764</t>
+          <t>6779</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10342,7 +10342,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4720</t>
+          <t>5025</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10377,7 +10377,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>957</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8511</t>
+          <t>9221</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10407,12 +10407,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,5%</t>
         </is>
       </c>
     </row>
@@ -10435,12 +10435,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>30392</t>
+          <t>30486</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>39136</t>
+          <t>39184</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10450,12 +10450,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10470,12 +10470,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>37607</t>
+          <t>37019</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>50068</t>
+          <t>50391</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10485,12 +10485,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10505,12 +10505,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>71877</t>
+          <t>72273</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>87072</t>
+          <t>87623</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10520,12 +10520,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>90,31%</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5316</t>
+          <t>5244</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10568,7 +10568,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3014</t>
+          <t>2274</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13431</t>
+          <t>12629</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10598,12 +10598,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10618,12 +10618,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3309</t>
+          <t>3176</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14496</t>
+          <t>14005</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10633,12 +10633,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,44%</t>
         </is>
       </c>
     </row>
@@ -10666,7 +10666,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6613</t>
+          <t>6925</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1111</t>
+          <t>1069</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10003</t>
+          <t>9465</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2963</t>
+          <t>2463</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>13568</t>
+          <t>12784</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,18%</t>
         </is>
       </c>
     </row>
@@ -10783,7 +10783,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4772</t>
+          <t>3924</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10798,7 +10798,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10813,12 +10813,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10632</t>
+          <t>9547</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10828,12 +10828,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10848,12 +10848,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>1959</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>11310</t>
+          <t>10402</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10863,12 +10863,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>18,03%</t>
         </is>
       </c>
     </row>
@@ -10891,12 +10891,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13188</t>
+          <t>12953</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20257</t>
+          <t>20276</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10906,12 +10906,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10926,12 +10926,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>24043</t>
+          <t>23738</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>34396</t>
+          <t>33590</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10941,12 +10941,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10961,12 +10961,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>40718</t>
+          <t>40386</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>51956</t>
+          <t>52509</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10976,12 +10976,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>91,0%</t>
         </is>
       </c>
     </row>
@@ -11009,7 +11009,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6201</t>
+          <t>6244</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11024,7 +11024,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11044,7 +11044,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5171</t>
+          <t>4367</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11059,7 +11059,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11079,7 +11079,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8797</t>
+          <t>7979</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11094,7 +11094,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>13,83%</t>
         </is>
       </c>
     </row>
@@ -11122,7 +11122,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>5106</t>
+          <t>4908</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11137,7 +11137,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -11157,7 +11157,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>5266</t>
+          <t>4243</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -11172,7 +11172,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -11192,7 +11192,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6517</t>
+          <t>5903</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -11207,7 +11207,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>10,23%</t>
         </is>
       </c>
     </row>
@@ -11239,7 +11239,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4409</t>
+          <t>5118</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11254,7 +11254,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11269,12 +11269,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1230</t>
+          <t>1228</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>10326</t>
+          <t>10247</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11284,12 +11284,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11304,12 +11304,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1582</t>
+          <t>2039</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>11743</t>
+          <t>11784</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11319,12 +11319,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,55%</t>
         </is>
       </c>
     </row>
@@ -11347,12 +11347,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4774</t>
+          <t>4983</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>11278</t>
+          <t>11583</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11362,12 +11362,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -11382,12 +11382,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>19546</t>
+          <t>19790</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>34149</t>
+          <t>35060</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -11397,12 +11397,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>78,09%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -11417,12 +11417,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>28252</t>
+          <t>27809</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>44555</t>
+          <t>43842</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -11432,12 +11432,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>76,44%</t>
         </is>
       </c>
     </row>
@@ -11495,12 +11495,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>6059</t>
+          <t>6218</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>20483</t>
+          <t>19328</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11510,12 +11510,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11530,12 +11530,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>5947</t>
+          <t>6245</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>19629</t>
+          <t>20392</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11545,12 +11545,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>35,56%</t>
         </is>
       </c>
     </row>
@@ -11578,7 +11578,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5935</t>
+          <t>5914</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11593,7 +11593,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11613,7 +11613,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6760</t>
+          <t>5837</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11628,7 +11628,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11648,7 +11648,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>10188</t>
+          <t>9245</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11663,7 +11663,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>16,12%</t>
         </is>
       </c>
     </row>
@@ -11690,12 +11690,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>10492</t>
+          <t>11538</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>28417</t>
+          <t>27798</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11705,12 +11705,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11725,12 +11725,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>14456</t>
+          <t>13903</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>34645</t>
+          <t>33511</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11740,12 +11740,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11760,12 +11760,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>30033</t>
+          <t>28981</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>55725</t>
+          <t>54461</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11775,12 +11775,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -11803,12 +11803,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>675867</t>
+          <t>674813</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>707739</t>
+          <t>705713</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11818,12 +11818,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11838,12 +11838,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>951264</t>
+          <t>950051</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>995468</t>
+          <t>994923</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11853,12 +11853,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -11873,12 +11873,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1636825</t>
+          <t>1636538</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1689541</t>
+          <t>1691819</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -11888,12 +11888,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,59%</t>
         </is>
       </c>
     </row>
@@ -11916,12 +11916,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>27325</t>
+          <t>28249</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>52759</t>
+          <t>52097</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -11931,12 +11931,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -11951,12 +11951,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>86790</t>
+          <t>85011</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>125425</t>
+          <t>125404</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -11986,12 +11986,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>122174</t>
+          <t>122813</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>171046</t>
+          <t>167237</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12001,12 +12001,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,95%</t>
         </is>
       </c>
     </row>
@@ -12029,12 +12029,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>5085</t>
+          <t>5009</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>18973</t>
+          <t>19007</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12044,7 +12044,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -12064,12 +12064,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>5318</t>
+          <t>5034</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>19067</t>
+          <t>18590</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12079,12 +12079,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12099,12 +12099,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>13685</t>
+          <t>12998</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>32176</t>
+          <t>32692</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -12114,12 +12114,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
